--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_atacama.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.69273400094705</v>
+      </c>
+      <c r="C2">
         <v>25.16704957996457</v>
-      </c>
-      <c r="C2">
-        <v>29.69273400094705</v>
       </c>
       <c r="D2">
         <v>3.973449477351916</v>
       </c>
       <c r="E2">
-        <v>16.25150765293122</v>
+        <v>19.17394775734857</v>
       </c>
       <c r="F2">
         <v>64.57454458972022</v>
       </c>
       <c r="G2">
-        <v>19.17394775734857</v>
+        <v>16.25150765293122</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.13639315869236</v>
+      </c>
+      <c r="C3">
         <v>30.5982535902432</v>
-      </c>
-      <c r="C3">
-        <v>30.13639315869236</v>
       </c>
       <c r="D3">
         <v>3.268160377358491</v>
       </c>
       <c r="E3">
-        <v>19.03650159385803</v>
+        <v>18.74915817357338</v>
       </c>
       <c r="F3">
         <v>62.21434023256858</v>
       </c>
       <c r="G3">
-        <v>18.74915817357338</v>
+        <v>19.03650159385803</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>34.86020226055919</v>
+      </c>
+      <c r="C4">
         <v>24.62819750148721</v>
-      </c>
-      <c r="C4">
-        <v>34.86020226055919</v>
       </c>
       <c r="D4">
         <v>4.060386473429952</v>
       </c>
       <c r="E4">
-        <v>15.4419992540097</v>
+        <v>21.85751585229392</v>
       </c>
       <c r="F4">
         <v>62.70048489369638</v>
       </c>
       <c r="G4">
-        <v>21.85751585229392</v>
+        <v>15.4419992540097</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>31.96776359973136</v>
+      </c>
+      <c r="C5">
         <v>32.56100291023058</v>
-      </c>
-      <c r="C5">
-        <v>31.96776359973136</v>
       </c>
       <c r="D5">
         <v>3.071158473702303</v>
       </c>
       <c r="E5">
-        <v>19.79046193618613</v>
+        <v>19.42989319001293</v>
       </c>
       <c r="F5">
         <v>60.77964487380094</v>
       </c>
       <c r="G5">
-        <v>19.42989319001293</v>
+        <v>19.79046193618613</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.69210203854294</v>
+      </c>
+      <c r="C6">
         <v>23.23716163529019</v>
-      </c>
-      <c r="C6">
-        <v>31.69210203854294</v>
       </c>
       <c r="D6">
         <v>4.303451581975072</v>
       </c>
       <c r="E6">
-        <v>14.99856197871728</v>
+        <v>20.45585274662065</v>
       </c>
       <c r="F6">
         <v>64.54558527466206</v>
       </c>
       <c r="G6">
-        <v>20.45585274662065</v>
+        <v>14.99856197871728</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.50777713768414</v>
+      </c>
+      <c r="C7">
         <v>32.53778838504375</v>
-      </c>
-      <c r="C7">
-        <v>30.50777713768414</v>
       </c>
       <c r="D7">
         <v>3.073349633251834</v>
       </c>
       <c r="E7">
+        <v>18.71119710608227</v>
+      </c>
+      <c r="F7">
+        <v>61.3325481618575</v>
+      </c>
+      <c r="G7">
         <v>19.95625473206023</v>
-      </c>
-      <c r="F7">
-        <v>61.33254816185749</v>
-      </c>
-      <c r="G7">
-        <v>18.71119710608227</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>31.37849679811257</v>
+      </c>
+      <c r="C8">
         <v>43.47826086956522</v>
-      </c>
-      <c r="C8">
-        <v>31.37849679811257</v>
       </c>
       <c r="D8">
         <v>2.3</v>
       </c>
       <c r="E8">
-        <v>24.8650732459522</v>
+        <v>17.94525828835775</v>
       </c>
       <c r="F8">
         <v>57.18966846569005</v>
       </c>
       <c r="G8">
-        <v>17.94525828835775</v>
+        <v>24.8650732459522</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.34751773049645</v>
+      </c>
+      <c r="C9">
         <v>32.42147922998987</v>
-      </c>
-      <c r="C9">
-        <v>31.34751773049645</v>
       </c>
       <c r="D9">
         <v>3.084375</v>
       </c>
       <c r="E9">
-        <v>19.79707993071022</v>
+        <v>19.14130165800544</v>
       </c>
       <c r="F9">
         <v>61.06161841128433</v>
       </c>
       <c r="G9">
-        <v>19.14130165800544</v>
+        <v>19.79707993071022</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.33280922431866</v>
+      </c>
+      <c r="C10">
         <v>34.53878406708596</v>
-      </c>
-      <c r="C10">
-        <v>30.33280922431866</v>
       </c>
       <c r="D10">
         <v>2.895295902883156</v>
       </c>
       <c r="E10">
+        <v>18.39783835333386</v>
+      </c>
+      <c r="F10">
+        <v>60.65326233807518</v>
+      </c>
+      <c r="G10">
         <v>20.94889930859096</v>
-      </c>
-      <c r="F10">
-        <v>60.65326233807519</v>
-      </c>
-      <c r="G10">
-        <v>18.39783835333386</v>
       </c>
     </row>
   </sheetData>
